--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624294</v>
       </c>
       <c r="B2" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624233</v>
       </c>
       <c r="B3" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624255</v>
       </c>
       <c r="B4" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624251</v>
+        <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>98734</v>
+        <v>96114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665187</v>
+        <v>665136</v>
       </c>
       <c r="R10" t="n">
-        <v>6703732</v>
+        <v>6703779</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,7 +1555,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624257</v>
+        <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>98734</v>
+        <v>96114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665084</v>
       </c>
       <c r="R11" t="n">
-        <v>6703755</v>
+        <v>6703823</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1671,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624232</v>
+        <v>129624251</v>
       </c>
       <c r="B12" t="n">
-        <v>96102</v>
+        <v>98746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665084</v>
+        <v>665187</v>
       </c>
       <c r="R12" t="n">
-        <v>6703823</v>
+        <v>6703732</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1750,6 +1749,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624235</v>
+        <v>129624257</v>
       </c>
       <c r="B13" t="n">
-        <v>96102</v>
+        <v>98746</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665136</v>
+        <v>665178</v>
       </c>
       <c r="R13" t="n">
-        <v>6703779</v>
+        <v>6703755</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1868,7 +1868,7 @@
         <v>129624246</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624294</v>
+        <v>129624233</v>
       </c>
       <c r="B2" t="n">
-        <v>100957</v>
+        <v>96115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665182</v>
+        <v>665097</v>
       </c>
       <c r="R2" t="n">
-        <v>6703734</v>
+        <v>6703818</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624233</v>
+        <v>129624294</v>
       </c>
       <c r="B3" t="n">
-        <v>96114</v>
+        <v>100958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665097</v>
+        <v>665182</v>
       </c>
       <c r="R3" t="n">
-        <v>6703818</v>
+        <v>6703734</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>129624255</v>
       </c>
       <c r="B4" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129624251</v>
       </c>
       <c r="B12" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>129624257</v>
       </c>
       <c r="B13" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129624246</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624273</v>
+        <v>129624242</v>
       </c>
       <c r="B8" t="n">
-        <v>96211</v>
+        <v>96115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,11 +1345,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1358,11 +1353,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1379,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624242</v>
+        <v>129624273</v>
       </c>
       <c r="B9" t="n">
-        <v>96115</v>
+        <v>96211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,6 +1442,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1460,6 +1455,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624243</v>
+        <v>129624292</v>
       </c>
       <c r="B17" t="n">
-        <v>96115</v>
+        <v>100958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R17" t="n">
-        <v>6703771</v>
+        <v>6703797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B18" t="n">
-        <v>100958</v>
+        <v>96115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R18" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624233</v>
       </c>
       <c r="B2" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624294</v>
       </c>
       <c r="B3" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624255</v>
       </c>
       <c r="B4" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624242</v>
+        <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96115</v>
+        <v>96216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,6 +1345,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1353,6 +1358,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1369,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624273</v>
+        <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96211</v>
+        <v>96120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,11 +1452,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1455,11 +1460,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1479,7 +1479,7 @@
         <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129624251</v>
       </c>
       <c r="B12" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>129624257</v>
       </c>
       <c r="B13" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,50 +1865,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R14" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1967,45 +1962,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B15" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>100958</v>
+        <v>96120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R17" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624243</v>
+        <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>96115</v>
+        <v>100963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R18" t="n">
-        <v>6703771</v>
+        <v>6703797</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624235</v>
+        <v>129624251</v>
       </c>
       <c r="B10" t="n">
-        <v>96120</v>
+        <v>98752</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665136</v>
+        <v>665187</v>
       </c>
       <c r="R10" t="n">
-        <v>6703779</v>
+        <v>6703732</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,6 +1555,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1573,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624232</v>
+        <v>129624257</v>
       </c>
       <c r="B11" t="n">
-        <v>96120</v>
+        <v>98752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665084</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703823</v>
+        <v>6703755</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1670,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624251</v>
+        <v>129624235</v>
       </c>
       <c r="B12" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665187</v>
+        <v>665136</v>
       </c>
       <c r="R12" t="n">
-        <v>6703732</v>
+        <v>6703779</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1749,7 +1750,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624257</v>
+        <v>129624232</v>
       </c>
       <c r="B13" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665178</v>
+        <v>665084</v>
       </c>
       <c r="R13" t="n">
-        <v>6703755</v>
+        <v>6703823</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1865,45 +1865,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B14" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1962,50 +1967,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R15" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624294</v>
+        <v>129624255</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665182</v>
+        <v>665198</v>
       </c>
       <c r="R3" t="n">
-        <v>6703734</v>
+        <v>6703797</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624255</v>
+        <v>129624294</v>
       </c>
       <c r="B4" t="n">
-        <v>98752</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665198</v>
+        <v>665182</v>
       </c>
       <c r="R4" t="n">
-        <v>6703797</v>
+        <v>6703734</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624233</v>
+        <v>129624294</v>
       </c>
       <c r="B2" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665097</v>
+        <v>665182</v>
       </c>
       <c r="R2" t="n">
-        <v>6703818</v>
+        <v>6703734</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624255</v>
+        <v>129624233</v>
       </c>
       <c r="B3" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665198</v>
+        <v>665097</v>
       </c>
       <c r="R3" t="n">
-        <v>6703797</v>
+        <v>6703818</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624294</v>
+        <v>129624255</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665182</v>
+        <v>665198</v>
       </c>
       <c r="R4" t="n">
-        <v>6703734</v>
+        <v>6703797</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624273</v>
+        <v>129624242</v>
       </c>
       <c r="B8" t="n">
-        <v>96216</v>
+        <v>96120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,11 +1345,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1358,11 +1353,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1379,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624242</v>
+        <v>129624273</v>
       </c>
       <c r="B9" t="n">
-        <v>96120</v>
+        <v>96216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,6 +1442,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1460,6 +1455,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624251</v>
+        <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665187</v>
+        <v>665136</v>
       </c>
       <c r="R10" t="n">
-        <v>6703732</v>
+        <v>6703779</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,7 +1555,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624257</v>
+        <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665084</v>
       </c>
       <c r="R11" t="n">
-        <v>6703755</v>
+        <v>6703823</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1671,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624235</v>
+        <v>129624257</v>
       </c>
       <c r="B12" t="n">
-        <v>96120</v>
+        <v>98752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665136</v>
+        <v>665178</v>
       </c>
       <c r="R12" t="n">
-        <v>6703779</v>
+        <v>6703755</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1768,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624232</v>
+        <v>129624251</v>
       </c>
       <c r="B13" t="n">
-        <v>96120</v>
+        <v>98752</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665084</v>
+        <v>665187</v>
       </c>
       <c r="R13" t="n">
-        <v>6703823</v>
+        <v>6703732</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1847,6 +1846,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624243</v>
+        <v>129624292</v>
       </c>
       <c r="B17" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R17" t="n">
-        <v>6703771</v>
+        <v>6703797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B18" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R18" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624294</v>
+        <v>129624233</v>
       </c>
       <c r="B2" t="n">
-        <v>100963</v>
+        <v>96124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665182</v>
+        <v>665097</v>
       </c>
       <c r="R2" t="n">
-        <v>6703734</v>
+        <v>6703818</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624233</v>
+        <v>129624255</v>
       </c>
       <c r="B3" t="n">
-        <v>96120</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665097</v>
+        <v>665198</v>
       </c>
       <c r="R3" t="n">
-        <v>6703818</v>
+        <v>6703797</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624255</v>
+        <v>129624294</v>
       </c>
       <c r="B4" t="n">
-        <v>98752</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665198</v>
+        <v>665182</v>
       </c>
       <c r="R4" t="n">
-        <v>6703797</v>
+        <v>6703734</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624242</v>
       </c>
       <c r="B8" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129624273</v>
       </c>
       <c r="B9" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624235</v>
+        <v>129624251</v>
       </c>
       <c r="B10" t="n">
-        <v>96120</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665136</v>
+        <v>665187</v>
       </c>
       <c r="R10" t="n">
-        <v>6703779</v>
+        <v>6703732</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,6 +1555,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1573,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624232</v>
+        <v>129624257</v>
       </c>
       <c r="B11" t="n">
-        <v>96120</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665084</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703823</v>
+        <v>6703755</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1670,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624257</v>
+        <v>129624235</v>
       </c>
       <c r="B12" t="n">
-        <v>98752</v>
+        <v>96124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665178</v>
+        <v>665136</v>
       </c>
       <c r="R12" t="n">
-        <v>6703755</v>
+        <v>6703779</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1767,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624251</v>
+        <v>129624232</v>
       </c>
       <c r="B13" t="n">
-        <v>98752</v>
+        <v>96124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1779,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665187</v>
+        <v>665084</v>
       </c>
       <c r="R13" t="n">
-        <v>6703732</v>
+        <v>6703823</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1846,7 +1847,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1865,50 +1865,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>100967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R14" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1967,45 +1962,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B15" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>100963</v>
+        <v>96124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R17" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624243</v>
+        <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>96120</v>
+        <v>100967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R18" t="n">
-        <v>6703771</v>
+        <v>6703797</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624233</v>
       </c>
       <c r="B2" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624255</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624294</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624242</v>
       </c>
       <c r="B8" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129624273</v>
       </c>
       <c r="B9" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624251</v>
+        <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>96126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665187</v>
+        <v>665136</v>
       </c>
       <c r="R10" t="n">
-        <v>6703732</v>
+        <v>6703779</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,7 +1555,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624257</v>
+        <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>96126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665084</v>
       </c>
       <c r="R11" t="n">
-        <v>6703755</v>
+        <v>6703823</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1671,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624235</v>
+        <v>129624251</v>
       </c>
       <c r="B12" t="n">
-        <v>96124</v>
+        <v>98758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1706,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665136</v>
+        <v>665187</v>
       </c>
       <c r="R12" t="n">
-        <v>6703779</v>
+        <v>6703732</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1750,6 +1749,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624232</v>
+        <v>129624257</v>
       </c>
       <c r="B13" t="n">
-        <v>96124</v>
+        <v>98758</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665084</v>
+        <v>665178</v>
       </c>
       <c r="R13" t="n">
-        <v>6703823</v>
+        <v>6703755</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1865,45 +1865,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B14" t="n">
-        <v>100967</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1962,50 +1967,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>100969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R15" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624242</v>
+        <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96126</v>
+        <v>96222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,6 +1345,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1353,6 +1358,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1369,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624273</v>
+        <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96222</v>
+        <v>96126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,11 +1452,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1455,11 +1460,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624233</v>
+        <v>129624294</v>
       </c>
       <c r="B2" t="n">
-        <v>96126</v>
+        <v>100979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665097</v>
+        <v>665182</v>
       </c>
       <c r="R2" t="n">
-        <v>6703818</v>
+        <v>6703734</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +775,7 @@
         <v>129624255</v>
       </c>
       <c r="B3" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624294</v>
+        <v>129624233</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>96136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665182</v>
+        <v>665097</v>
       </c>
       <c r="R4" t="n">
-        <v>6703734</v>
+        <v>6703818</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129624251</v>
       </c>
       <c r="B12" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>129624257</v>
       </c>
       <c r="B13" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624273</v>
+        <v>129624242</v>
       </c>
       <c r="B8" t="n">
-        <v>96232</v>
+        <v>96136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,11 +1345,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1358,11 +1353,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1379,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624242</v>
+        <v>129624273</v>
       </c>
       <c r="B9" t="n">
-        <v>96136</v>
+        <v>96232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,6 +1442,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1460,6 +1455,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1865,50 +1865,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R14" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1967,45 +1962,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B15" t="n">
-        <v>100979</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624294</v>
+        <v>129624255</v>
       </c>
       <c r="B2" t="n">
-        <v>100979</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665182</v>
+        <v>665198</v>
       </c>
       <c r="R2" t="n">
-        <v>6703734</v>
+        <v>6703797</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624255</v>
+        <v>129624294</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>100979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665198</v>
+        <v>665182</v>
       </c>
       <c r="R3" t="n">
-        <v>6703797</v>
+        <v>6703734</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624242</v>
+        <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96136</v>
+        <v>96232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,6 +1345,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1353,6 +1358,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1369,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624273</v>
+        <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96232</v>
+        <v>96136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,11 +1452,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1455,11 +1460,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624255</v>
+        <v>129624233</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>96140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665198</v>
+        <v>665097</v>
       </c>
       <c r="R2" t="n">
-        <v>6703797</v>
+        <v>6703818</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +775,7 @@
         <v>129624294</v>
       </c>
       <c r="B3" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624233</v>
+        <v>129624255</v>
       </c>
       <c r="B4" t="n">
-        <v>96136</v>
+        <v>98772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665097</v>
+        <v>665198</v>
       </c>
       <c r="R4" t="n">
-        <v>6703818</v>
+        <v>6703797</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129624235</v>
       </c>
       <c r="B10" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>129624232</v>
       </c>
       <c r="B11" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129624251</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>129624257</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,45 +1865,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B14" t="n">
-        <v>100979</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1962,50 +1967,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>100983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R15" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624243</v>
+        <v>129624292</v>
       </c>
       <c r="B17" t="n">
-        <v>96136</v>
+        <v>100983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R17" t="n">
-        <v>6703771</v>
+        <v>6703797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B18" t="n">
-        <v>100979</v>
+        <v>96140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R18" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624233</v>
+        <v>129624294</v>
       </c>
       <c r="B2" t="n">
-        <v>96140</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665097</v>
+        <v>665182</v>
       </c>
       <c r="R2" t="n">
-        <v>6703818</v>
+        <v>6703734</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624294</v>
+        <v>129624255</v>
       </c>
       <c r="B3" t="n">
-        <v>100983</v>
+        <v>98772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665182</v>
+        <v>665198</v>
       </c>
       <c r="R3" t="n">
-        <v>6703734</v>
+        <v>6703797</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624255</v>
+        <v>129624233</v>
       </c>
       <c r="B4" t="n">
-        <v>98772</v>
+        <v>96140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665198</v>
+        <v>665097</v>
       </c>
       <c r="R4" t="n">
-        <v>6703797</v>
+        <v>6703818</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624294</v>
+        <v>129624255</v>
       </c>
       <c r="B2" t="n">
-        <v>100983</v>
+        <v>98775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665182</v>
+        <v>665198</v>
       </c>
       <c r="R2" t="n">
-        <v>6703734</v>
+        <v>6703797</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624255</v>
+        <v>129624294</v>
       </c>
       <c r="B3" t="n">
-        <v>98772</v>
+        <v>100986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665198</v>
+        <v>665182</v>
       </c>
       <c r="R3" t="n">
-        <v>6703797</v>
+        <v>6703734</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>129624233</v>
       </c>
       <c r="B4" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129624241</v>
       </c>
       <c r="B6" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129624244</v>
       </c>
       <c r="B7" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129624273</v>
       </c>
       <c r="B8" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129624242</v>
       </c>
       <c r="B9" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624235</v>
+        <v>129624251</v>
       </c>
       <c r="B10" t="n">
-        <v>96140</v>
+        <v>98775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665136</v>
+        <v>665187</v>
       </c>
       <c r="R10" t="n">
-        <v>6703779</v>
+        <v>6703732</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,6 +1555,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1573,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624232</v>
+        <v>129624257</v>
       </c>
       <c r="B11" t="n">
-        <v>96140</v>
+        <v>98775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665084</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703823</v>
+        <v>6703755</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1670,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624251</v>
+        <v>129624235</v>
       </c>
       <c r="B12" t="n">
-        <v>98772</v>
+        <v>96143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665187</v>
+        <v>665136</v>
       </c>
       <c r="R12" t="n">
-        <v>6703732</v>
+        <v>6703779</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1749,7 +1750,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624257</v>
+        <v>129624232</v>
       </c>
       <c r="B13" t="n">
-        <v>98772</v>
+        <v>96143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665178</v>
+        <v>665084</v>
       </c>
       <c r="R13" t="n">
-        <v>6703755</v>
+        <v>6703823</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1865,50 +1865,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>100986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R14" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1967,45 +1962,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B15" t="n">
-        <v>100983</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2067,7 +2067,7 @@
         <v>129624256</v>
       </c>
       <c r="B16" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129624292</v>
       </c>
       <c r="B17" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129624243</v>
       </c>
       <c r="B18" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -1865,45 +1865,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624293</v>
+        <v>129624246</v>
       </c>
       <c r="B14" t="n">
-        <v>100986</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665200</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703770</v>
+        <v>6703786</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1962,50 +1967,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624246</v>
+        <v>129624293</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>100986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665200</v>
       </c>
       <c r="R15" t="n">
-        <v>6703786</v>
+        <v>6703770</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B17" t="n">
-        <v>100986</v>
+        <v>96143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R17" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624243</v>
+        <v>129624292</v>
       </c>
       <c r="B18" t="n">
-        <v>96143</v>
+        <v>100986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R18" t="n">
-        <v>6703771</v>
+        <v>6703797</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92058</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129624259</v>
       </c>
       <c r="B5" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624255</v>
+        <v>129624224</v>
       </c>
       <c r="B2" t="n">
-        <v>98775</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R2" t="n">
-        <v>6703797</v>
+        <v>6703804</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624294</v>
+        <v>129624271</v>
       </c>
       <c r="B3" t="n">
-        <v>100986</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665182</v>
+        <v>665238</v>
       </c>
       <c r="R3" t="n">
-        <v>6703734</v>
+        <v>6703837</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624233</v>
+        <v>129624272</v>
       </c>
       <c r="B4" t="n">
-        <v>96143</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665097</v>
+        <v>665227</v>
       </c>
       <c r="R4" t="n">
-        <v>6703818</v>
+        <v>6703829</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624259</v>
+        <v>129624273</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665200</v>
+        <v>665207</v>
       </c>
       <c r="R5" t="n">
-        <v>6703786</v>
+        <v>6703784</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1039,6 +1054,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1048,19 +1068,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1078,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624241</v>
+        <v>129624259</v>
       </c>
       <c r="B6" t="n">
-        <v>96143</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665201</v>
+        <v>665200</v>
       </c>
       <c r="R6" t="n">
-        <v>6703797</v>
+        <v>6703786</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,6 +1169,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1175,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624244</v>
+        <v>129624231</v>
       </c>
       <c r="B7" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665182</v>
+        <v>665273</v>
       </c>
       <c r="R7" t="n">
-        <v>6703749</v>
+        <v>6703827</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1272,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624273</v>
+        <v>129624232</v>
       </c>
       <c r="B8" t="n">
-        <v>96239</v>
+        <v>96458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665207</v>
+        <v>665084</v>
       </c>
       <c r="R8" t="n">
-        <v>6703784</v>
+        <v>6703823</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1345,11 +1370,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>dikad</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1358,11 +1378,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrsumpskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1379,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624242</v>
+        <v>129624233</v>
       </c>
       <c r="B9" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665207</v>
+        <v>665097</v>
       </c>
       <c r="R9" t="n">
-        <v>6703784</v>
+        <v>6703818</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1476,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624251</v>
+        <v>129624234</v>
       </c>
       <c r="B10" t="n">
-        <v>98775</v>
+        <v>96458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665187</v>
+        <v>665142</v>
       </c>
       <c r="R10" t="n">
-        <v>6703732</v>
+        <v>6703802</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,7 +1570,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624257</v>
+        <v>129624235</v>
       </c>
       <c r="B11" t="n">
-        <v>98775</v>
+        <v>96458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1609,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665136</v>
       </c>
       <c r="R11" t="n">
-        <v>6703755</v>
+        <v>6703779</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1671,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624235</v>
+        <v>129624237</v>
       </c>
       <c r="B12" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665136</v>
+        <v>665235</v>
       </c>
       <c r="R12" t="n">
-        <v>6703779</v>
+        <v>6703837</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1768,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624232</v>
+        <v>129624238</v>
       </c>
       <c r="B13" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665084</v>
+        <v>665241</v>
       </c>
       <c r="R13" t="n">
-        <v>6703823</v>
+        <v>6703839</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1865,50 +1879,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624246</v>
+        <v>129624239</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665227</v>
       </c>
       <c r="R14" t="n">
-        <v>6703786</v>
+        <v>6703829</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1967,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624293</v>
+        <v>129624240</v>
       </c>
       <c r="B15" t="n">
-        <v>100986</v>
+        <v>96458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665200</v>
+        <v>665198</v>
       </c>
       <c r="R15" t="n">
-        <v>6703770</v>
+        <v>6703801</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2064,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624256</v>
+        <v>129624241</v>
       </c>
       <c r="B16" t="n">
-        <v>98775</v>
+        <v>96458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665203</v>
+        <v>665201</v>
       </c>
       <c r="R16" t="n">
-        <v>6703763</v>
+        <v>6703797</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2161,10 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624243</v>
+        <v>129624242</v>
       </c>
       <c r="B17" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,10 +2205,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665200</v>
+        <v>665207</v>
       </c>
       <c r="R17" t="n">
-        <v>6703771</v>
+        <v>6703784</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2258,10 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624292</v>
+        <v>129624243</v>
       </c>
       <c r="B18" t="n">
-        <v>100986</v>
+        <v>96458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2278,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665198</v>
+        <v>665200</v>
       </c>
       <c r="R18" t="n">
-        <v>6703797</v>
+        <v>6703771</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2352,6 +2361,1977 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129624244</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>665182</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6703749</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129624230</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>665217</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6703818</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129624246</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>665142</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6703786</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129624282</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>665066</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6703824</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129624229</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>665157</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6703792</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129624251</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>665187</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6703732</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129624252</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>665269</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6703827</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129624253</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>665178</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6703813</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129624254</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>665212</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6703814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129624255</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>665198</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6703797</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129624256</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>665203</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6703763</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129624257</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>665178</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6703755</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129624295</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>665247</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6703823</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129624286</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>665264</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6703843</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129624288</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>665061</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6703834</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129624290</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>665221</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6703828</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129624291</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>665217</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6703817</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129624292</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>665198</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6703797</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129624293</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>665200</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703770</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129624294</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>665182</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6703734</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49888-2025 artfynd.xlsx
+++ b/artfynd/A 49888-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624272</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624273</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624231</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624232</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624233</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624234</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624235</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624237</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624238</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624239</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624240</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624241</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624242</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624243</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2555,6 +2650,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624230</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2657,6 +2757,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624246</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2774,6 +2879,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624282</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2876,6 +2986,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624229</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2974,6 +3089,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624251</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3071,6 +3191,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624252</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3168,6 +3293,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624253</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3265,6 +3395,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624254</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3362,6 +3497,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624255</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3459,6 +3599,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624256</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3556,6 +3701,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624257</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3653,6 +3803,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624295</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3750,6 +3905,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624286</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3847,6 +4007,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624288</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3944,6 +4109,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624290</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4041,6 +4211,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624291</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4138,6 +4313,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624292</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4235,6 +4415,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624293</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4332,8 +4517,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>